--- a/features/testdata/contractor_employee.xlsx
+++ b/features/testdata/contractor_employee.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CLMS-Automation\testing-framework-playwright--simplecode\features\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2032652E-171D-4A28-A574-054677BC1439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A40840-4D8C-454D-9E4A-440E6D058662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ContratorEmployee" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="205">
   <si>
     <t>EmployeeCode</t>
   </si>
@@ -483,9 +483,6 @@
     <t>IsAutoShiftApplicable</t>
   </si>
   <si>
-    <t>Sharma</t>
-  </si>
-  <si>
     <t>K</t>
   </si>
   <si>
@@ -549,24 +546,12 @@
     <t>Semi-Skilled</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
     <t>OT Applicable</t>
   </si>
   <si>
     <t>Hinduism</t>
   </si>
   <si>
-    <t xml:space="preserve">Isha </t>
-  </si>
-  <si>
-    <t>Rana</t>
-  </si>
-  <si>
     <t>A+</t>
   </si>
   <si>
@@ -594,9 +579,6 @@
     <t>Manish</t>
   </si>
   <si>
-    <t>Mandavkar</t>
-  </si>
-  <si>
     <t>Waghare</t>
   </si>
   <si>
@@ -631,6 +613,33 @@
   </si>
   <si>
     <t>Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Ganu</t>
+  </si>
+  <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>Kapila</t>
+  </si>
+  <si>
+    <t>Bhophalekar</t>
+  </si>
+  <si>
+    <t>Jaydev</t>
+  </si>
+  <si>
+    <t>Tejpal</t>
+  </si>
+  <si>
+    <t>Marajkar</t>
+  </si>
+  <si>
+    <t>T</t>
   </si>
 </sst>
 </file>
@@ -678,8 +687,8 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1154,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EV13"/>
+  <dimension ref="A1:EV15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1755,37 +1764,37 @@
     </row>
     <row r="2" spans="1:152" ht="15.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>66736632476</v>
+        <v>283076</v>
       </c>
       <c r="B2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" t="s">
         <v>152</v>
-      </c>
-      <c r="D2" t="s">
-        <v>153</v>
       </c>
       <c r="G2" s="1">
         <v>32697</v>
       </c>
       <c r="H2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I2" t="s">
         <v>154</v>
       </c>
-      <c r="I2" t="s">
-        <v>155</v>
-      </c>
       <c r="J2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M2" t="s">
         <v>157</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>158</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>159</v>
-      </c>
-      <c r="O2" t="s">
-        <v>160</v>
       </c>
       <c r="P2" s="1">
         <v>46044</v>
@@ -1793,235 +1802,247 @@
       <c r="Q2">
         <v>199</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>161</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>162</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AI2" t="s">
         <v>163</v>
       </c>
-      <c r="AI2" t="s">
-        <v>164</v>
-      </c>
       <c r="AJ2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AK2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AN2" t="s">
         <v>164</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AV2" t="s">
         <v>165</v>
       </c>
-      <c r="AO2" t="s">
-        <v>164</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>165</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>164</v>
-      </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>166</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>167</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>169</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC2" t="s">
         <v>170</v>
       </c>
-      <c r="BB2" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>171</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>172</v>
       </c>
-      <c r="BE2" t="s">
-        <v>173</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>174</v>
+      <c r="BF2">
+        <v>1000</v>
       </c>
       <c r="BG2" s="1">
         <v>46228</v>
       </c>
-      <c r="BH2" t="s">
-        <v>175</v>
+      <c r="BH2">
+        <v>1004</v>
       </c>
       <c r="BQ2" s="3">
-        <v>965236585254</v>
+        <v>566290101877</v>
       </c>
       <c r="CY2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DA2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DC2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DE2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DG2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DI2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DS2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DT2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DU2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DV2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="DW2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="DX2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="DY2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="DZ2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="EA2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EB2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EC2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="ED2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="EF2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="EH2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="EJ2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EK2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="EL2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EU2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="EV2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:152" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>32476</v>
+        <v>950090</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="G3" s="1">
-        <v>32831</v>
+        <v>34657</v>
       </c>
       <c r="H3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J3" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="K3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M3" t="s">
         <v>157</v>
       </c>
-      <c r="M3" t="s">
-        <v>158</v>
+      <c r="N3" t="s">
+        <v>194</v>
       </c>
       <c r="O3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P3" s="1">
-        <v>46056</v>
+        <v>46068</v>
       </c>
       <c r="Q3">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="T3" t="s">
+        <v>161</v>
+      </c>
+      <c r="U3" t="s">
         <v>162</v>
       </c>
-      <c r="U3" t="s">
+      <c r="AJ3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO3" t="s">
         <v>163</v>
       </c>
+      <c r="AP3" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>160</v>
+      </c>
       <c r="AR3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AT3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AV3" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW3" t="s">
         <v>166</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AX3" t="s">
         <v>167</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AY3" t="s">
         <v>168</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="BA3" t="s">
         <v>169</v>
       </c>
-      <c r="BA3" t="s">
+      <c r="BB3" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC3" t="s">
         <v>170</v>
       </c>
-      <c r="BB3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC3" t="s">
+      <c r="BD3" t="s">
         <v>171</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
         <v>172</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>173</v>
       </c>
       <c r="BF3">
         <v>1001</v>
@@ -2031,7 +2052,7 @@
         <v>1004</v>
       </c>
       <c r="BQ3" s="3">
-        <v>961201180204</v>
+        <v>555200103430</v>
       </c>
     </row>
     <row r="4" spans="1:152" x14ac:dyDescent="0.25">
@@ -2039,362 +2060,359 @@
         <v>556700</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G4" s="5">
+        <v>185</v>
+      </c>
+      <c r="G4" s="4">
         <v>32831</v>
       </c>
       <c r="H4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J4" t="s">
+        <v>155</v>
+      </c>
+      <c r="K4" t="s">
         <v>156</v>
       </c>
-      <c r="K4" t="s">
-        <v>157</v>
-      </c>
       <c r="AV4" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW4" t="s">
         <v>166</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>167</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>168</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="BA4" t="s">
         <v>169</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC4" t="s">
         <v>170</v>
       </c>
-      <c r="BB4" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>171</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>172</v>
       </c>
       <c r="BF4">
         <v>1001</v>
       </c>
-      <c r="BG4" s="4"/>
+      <c r="BG4" s="2"/>
       <c r="BH4">
         <v>1004</v>
       </c>
       <c r="BQ4" s="3">
-        <v>901201180204</v>
+        <v>50802111</v>
       </c>
     </row>
     <row r="5" spans="1:152" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G5" s="4">
+        <v>32528</v>
+      </c>
+      <c r="H5" t="s">
         <v>191</v>
       </c>
-      <c r="G5" s="5">
-        <v>32528</v>
-      </c>
-      <c r="H5" t="s">
-        <v>197</v>
-      </c>
       <c r="J5" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="K5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AV5" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW5" t="s">
         <v>166</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>167</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>168</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="BA5" t="s">
         <v>169</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BB5" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC5" t="s">
         <v>170</v>
       </c>
-      <c r="BB5" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC5" t="s">
+      <c r="BD5" t="s">
         <v>171</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>172</v>
       </c>
       <c r="BF5">
         <v>1001</v>
       </c>
-      <c r="BG5" s="4"/>
+      <c r="BG5" s="2"/>
       <c r="BH5">
         <v>1004</v>
       </c>
       <c r="BQ5" s="3">
-        <v>962201180204</v>
+        <v>20101803</v>
       </c>
     </row>
     <row r="6" spans="1:152" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="4">
+        <v>32833</v>
+      </c>
+      <c r="H6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" s="4">
+        <v>32831</v>
+      </c>
+      <c r="N6" t="s">
         <v>194</v>
       </c>
-      <c r="G6" s="5">
-        <v>32833</v>
-      </c>
-      <c r="H6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K6" t="s">
-        <v>157</v>
-      </c>
-      <c r="L6" s="5">
-        <v>32831</v>
-      </c>
-      <c r="N6" t="s">
-        <v>200</v>
-      </c>
       <c r="O6" t="s">
-        <v>160</v>
-      </c>
-      <c r="P6" s="5">
+        <v>159</v>
+      </c>
+      <c r="P6" s="4">
         <v>46035</v>
       </c>
       <c r="Q6">
         <v>562</v>
       </c>
       <c r="AV6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW6" t="s">
         <v>166</v>
       </c>
-      <c r="AW6" t="s">
+      <c r="AX6" t="s">
         <v>167</v>
       </c>
-      <c r="AX6" t="s">
+      <c r="AY6" t="s">
         <v>168</v>
       </c>
-      <c r="AY6" t="s">
+      <c r="BA6" t="s">
         <v>169</v>
       </c>
-      <c r="BA6" t="s">
+      <c r="BB6" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC6" t="s">
         <v>170</v>
       </c>
-      <c r="BB6" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC6" t="s">
+      <c r="BD6" t="s">
         <v>171</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>172</v>
       </c>
       <c r="BF6">
         <v>1001</v>
       </c>
-      <c r="BG6" s="4"/>
+      <c r="BG6" s="2"/>
       <c r="BH6">
         <v>1004</v>
       </c>
-      <c r="BQ6" s="3">
-        <v>961001180204</v>
-      </c>
+      <c r="BQ6" s="3"/>
     </row>
     <row r="7" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>9</v>
+      </c>
       <c r="B7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G7" s="4">
+        <v>36412</v>
+      </c>
+      <c r="H7" t="s">
+        <v>191</v>
+      </c>
+      <c r="J7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K7" t="s">
+        <v>156</v>
+      </c>
+      <c r="L7" s="4">
+        <v>32831</v>
+      </c>
+      <c r="N7" t="s">
+        <v>194</v>
+      </c>
+      <c r="O7" t="s">
         <v>195</v>
       </c>
-      <c r="D7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G7" s="5">
-        <v>36412</v>
-      </c>
-      <c r="H7" t="s">
-        <v>197</v>
-      </c>
-      <c r="J7" t="s">
-        <v>156</v>
-      </c>
-      <c r="K7" t="s">
-        <v>157</v>
-      </c>
-      <c r="L7" s="5">
-        <v>32831</v>
-      </c>
-      <c r="N7" t="s">
-        <v>200</v>
-      </c>
-      <c r="O7" t="s">
-        <v>201</v>
-      </c>
-      <c r="P7" s="5">
+      <c r="P7" s="4">
         <v>45691</v>
       </c>
       <c r="Q7">
         <v>123</v>
       </c>
       <c r="R7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AV7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW7" t="s">
         <v>166</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AX7" t="s">
         <v>167</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AY7" t="s">
         <v>168</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="BA7" t="s">
         <v>169</v>
       </c>
-      <c r="BA7" t="s">
+      <c r="BB7" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC7" t="s">
         <v>170</v>
       </c>
-      <c r="BB7" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC7" t="s">
+      <c r="BD7" t="s">
         <v>171</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>172</v>
       </c>
       <c r="BF7">
         <v>1001</v>
       </c>
-      <c r="BG7" s="4"/>
+      <c r="BG7" s="2"/>
       <c r="BH7">
         <v>1004</v>
       </c>
-      <c r="BQ7" s="3">
-        <v>961201180200</v>
-      </c>
+      <c r="BQ7" s="3"/>
     </row>
     <row r="8" spans="1:152" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>32477</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
-      </c>
-      <c r="G8" s="5">
+        <v>178</v>
+      </c>
+      <c r="G8" s="4">
         <v>32835</v>
       </c>
       <c r="H8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J8" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AV8" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW8" t="s">
         <v>166</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AX8" t="s">
         <v>167</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="AY8" t="s">
         <v>168</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="BA8" t="s">
         <v>169</v>
       </c>
-      <c r="BA8" t="s">
+      <c r="BB8" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC8" t="s">
         <v>170</v>
       </c>
-      <c r="BB8" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC8" t="s">
+      <c r="BD8" t="s">
         <v>171</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>172</v>
       </c>
       <c r="BF8">
         <v>1001</v>
       </c>
-      <c r="BG8" s="4"/>
+      <c r="BG8" s="2"/>
       <c r="BH8">
         <v>1004</v>
       </c>
-      <c r="BQ8" s="3">
-        <v>761201180204</v>
-      </c>
+      <c r="BQ8" s="3"/>
     </row>
     <row r="9" spans="1:152" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>32478</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
-      </c>
-      <c r="G9" s="5">
+        <v>180</v>
+      </c>
+      <c r="G9" s="4">
         <v>32836</v>
       </c>
       <c r="H9" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AV9" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW9" t="s">
         <v>166</v>
       </c>
-      <c r="AW9" t="s">
+      <c r="AX9" t="s">
         <v>167</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AY9" t="s">
         <v>168</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="BA9" t="s">
         <v>169</v>
       </c>
-      <c r="BA9" t="s">
+      <c r="BB9" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC9" t="s">
         <v>170</v>
       </c>
-      <c r="BB9" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC9" t="s">
+      <c r="BD9" t="s">
         <v>171</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>172</v>
       </c>
       <c r="BF9">
         <v>1001</v>
       </c>
-      <c r="BG9" s="4"/>
+      <c r="BG9" s="2"/>
       <c r="BH9">
         <v>1004</v>
       </c>
       <c r="BQ9" s="3">
-        <v>661201180206</v>
+        <v>500210101997</v>
       </c>
     </row>
     <row r="10" spans="1:152" x14ac:dyDescent="0.25">
@@ -2402,138 +2420,305 @@
         <v>30479</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>187</v>
-      </c>
-      <c r="G10" s="5">
+        <v>182</v>
+      </c>
+      <c r="G10" s="4">
         <v>32837</v>
       </c>
       <c r="H10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AV10" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW10" t="s">
         <v>166</v>
       </c>
-      <c r="AW10" t="s">
+      <c r="AX10" t="s">
         <v>167</v>
       </c>
-      <c r="AX10" t="s">
+      <c r="AY10" t="s">
         <v>168</v>
       </c>
-      <c r="AY10" t="s">
+      <c r="BA10" t="s">
         <v>169</v>
       </c>
-      <c r="BA10" t="s">
+      <c r="BB10" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC10" t="s">
         <v>170</v>
       </c>
-      <c r="BB10" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC10" t="s">
+      <c r="BD10" t="s">
         <v>171</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>172</v>
       </c>
       <c r="BF10">
         <v>1001</v>
       </c>
-      <c r="BG10" s="4"/>
+      <c r="BG10" s="2"/>
       <c r="BH10">
         <v>1004</v>
       </c>
-      <c r="BQ10" s="3">
-        <v>999201180204</v>
-      </c>
+      <c r="BQ10" s="3"/>
     </row>
     <row r="11" spans="1:152" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>32479</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D11" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="AV11" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW11" t="s">
         <v>166</v>
       </c>
-      <c r="AW11" t="s">
+      <c r="AX11" t="s">
         <v>167</v>
       </c>
-      <c r="AX11" t="s">
+      <c r="AY11" t="s">
         <v>168</v>
       </c>
-      <c r="AY11" t="s">
+      <c r="BA11" t="s">
         <v>169</v>
       </c>
-      <c r="BA11" t="s">
+      <c r="BB11" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC11" t="s">
         <v>170</v>
       </c>
-      <c r="BB11" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC11" t="s">
+      <c r="BD11" t="s">
         <v>171</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>172</v>
       </c>
       <c r="BF11">
         <v>1001</v>
       </c>
-      <c r="BG11" s="4"/>
+      <c r="BG11" s="2"/>
       <c r="BH11">
         <v>1004</v>
       </c>
       <c r="BQ11" s="3">
-        <v>456781180204</v>
+        <v>500210100800</v>
       </c>
     </row>
     <row r="12" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>76678888888</v>
+      </c>
+      <c r="B12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" s="4">
+        <v>47290</v>
+      </c>
+      <c r="H12" t="s">
+        <v>153</v>
+      </c>
+      <c r="I12" t="s">
+        <v>154</v>
+      </c>
+      <c r="J12" t="s">
+        <v>192</v>
+      </c>
+      <c r="M12" t="s">
+        <v>157</v>
+      </c>
+      <c r="N12" t="s">
+        <v>158</v>
+      </c>
+      <c r="O12" t="s">
+        <v>159</v>
+      </c>
+      <c r="P12" s="4">
+        <v>44209</v>
+      </c>
+      <c r="Q12">
+        <v>4088</v>
+      </c>
+      <c r="T12" t="s">
+        <v>161</v>
+      </c>
+      <c r="U12" t="s">
+        <v>162</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>163</v>
+      </c>
       <c r="AV12" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW12" t="s">
         <v>166</v>
       </c>
-      <c r="AW12" t="s">
+      <c r="AX12" t="s">
         <v>167</v>
       </c>
-      <c r="AX12" t="s">
+      <c r="AY12" t="s">
         <v>168</v>
       </c>
-      <c r="AY12" t="s">
+      <c r="BA12" t="s">
         <v>169</v>
       </c>
-      <c r="BA12" t="s">
+      <c r="BB12" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC12" t="s">
         <v>170</v>
       </c>
-      <c r="BB12" t="s">
-        <v>181</v>
-      </c>
-      <c r="BC12" t="s">
+      <c r="BD12" t="s">
         <v>171</v>
       </c>
-      <c r="BD12" t="s">
+      <c r="BE12" t="s">
         <v>172</v>
       </c>
       <c r="BF12">
         <v>1001</v>
       </c>
-      <c r="BG12" s="4"/>
+      <c r="BG12" s="2">
+        <v>46157</v>
+      </c>
       <c r="BH12">
         <v>1004</v>
       </c>
+      <c r="BP12" s="5">
+        <v>121245349865</v>
+      </c>
       <c r="BQ12" s="3">
-        <v>900200080204</v>
+        <v>604010107770</v>
+      </c>
+      <c r="DC12" t="s">
+        <v>160</v>
+      </c>
+      <c r="DU12" t="s">
+        <v>160</v>
+      </c>
+      <c r="ED12" t="s">
+        <v>160</v>
+      </c>
+      <c r="EJ12" t="s">
+        <v>163</v>
+      </c>
+      <c r="EV12" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="BG13" s="4"/>
+      <c r="B13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" t="s">
+        <v>203</v>
+      </c>
+      <c r="G13" s="1">
+        <v>38310</v>
+      </c>
+      <c r="H13" t="s">
+        <v>153</v>
+      </c>
+      <c r="J13" t="s">
+        <v>192</v>
+      </c>
+      <c r="K13" t="s">
+        <v>156</v>
+      </c>
+      <c r="M13" t="s">
+        <v>157</v>
+      </c>
+      <c r="N13" t="s">
+        <v>194</v>
+      </c>
+      <c r="O13" t="s">
+        <v>159</v>
+      </c>
+      <c r="P13" s="1">
+        <v>45703</v>
+      </c>
+      <c r="Q13">
+        <v>177</v>
+      </c>
+      <c r="T13" t="s">
+        <v>161</v>
+      </c>
+      <c r="U13" t="s">
+        <v>162</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>163</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>164</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>163</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>166</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>167</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>168</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>169</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>170</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>171</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BF13">
+        <v>1001</v>
+      </c>
+      <c r="BG13" s="2">
+        <v>46037</v>
+      </c>
+      <c r="BH13">
+        <v>1004</v>
+      </c>
+      <c r="BQ13" s="3"/>
+      <c r="EF13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>196</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
